--- a/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_23_8.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_23_8.xlsx
@@ -513,111 +513,111 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_0</t>
+          <t>model_23_8_1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9949886032723484</v>
+        <v>0.9997732507292887</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7396423457227064</v>
+        <v>0.7099302795942648</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9775012387041988</v>
+        <v>0.9999966257932638</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9916921122620866</v>
+        <v>0.9980198515449996</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9850955323261154</v>
+        <v>0.9998270790293392</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03351123299316677</v>
+        <v>0.0001346081621526972</v>
       </c>
       <c r="H2" t="n">
-        <v>1.741012832989027</v>
+        <v>0.1721979163923205</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1210072281577724</v>
+        <v>3.320757451707956e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04933334676419511</v>
+        <v>0.0002260644195962692</v>
       </c>
       <c r="K2" t="n">
-        <v>0.08517027999681606</v>
+        <v>0.000114689598327516</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1959539239744956</v>
+        <v>0.002490921722587949</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1830607358041772</v>
+        <v>0.01160207576913275</v>
       </c>
       <c r="N2" t="n">
-        <v>1.003436386327533</v>
+        <v>1.000155485214202</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1908540103153249</v>
+        <v>0.0120960001542325</v>
       </c>
       <c r="P2" t="n">
-        <v>124.7917491662543</v>
+        <v>135.8262850050551</v>
       </c>
       <c r="Q2" t="n">
-        <v>196.7054228334782</v>
+        <v>207.739958672279</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_1</t>
+          <t>model_23_8_0</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9952329408347028</v>
+        <v>0.9997729042618807</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7387076958526052</v>
+        <v>0.7099189256082213</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9785275289277369</v>
+        <v>0.9999966746640441</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9912318215226055</v>
+        <v>0.998020929730955</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9853393362028968</v>
+        <v>0.9998272013208217</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03187734658863153</v>
+        <v>0.0001348138401726944</v>
       </c>
       <c r="H3" t="n">
-        <v>1.747262840974061</v>
+        <v>0.1722046566089026</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1154874338187419</v>
+        <v>3.272660811314534e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0520666146391988</v>
+        <v>0.0002259413280767414</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08377708401664889</v>
+        <v>0.0001146084886682967</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1818352121449851</v>
+        <v>0.002484036603077944</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1785422823552772</v>
+        <v>0.01161093623153165</v>
       </c>
       <c r="N3" t="n">
-        <v>1.003268840570489</v>
+        <v>1.000155722791853</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1861431969486171</v>
+        <v>0.01210523782485941</v>
       </c>
       <c r="P3" t="n">
-        <v>124.8917193194928</v>
+        <v>135.8232313857044</v>
       </c>
       <c r="Q3" t="n">
-        <v>196.8053929867166</v>
+        <v>207.7369050529283</v>
       </c>
     </row>
     <row r="4">
@@ -627,52 +627,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9954297903994082</v>
+        <v>0.9998183967588591</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7378496274619734</v>
+        <v>0.7094850620875969</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9794128579772614</v>
+        <v>0.9999984016784834</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9908023764883863</v>
+        <v>0.9984559972565147</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9855328392788418</v>
+        <v>0.9998659310111313</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03056101264303781</v>
+        <v>0.000107807528792762</v>
       </c>
       <c r="H4" t="n">
-        <v>1.753000748253257</v>
+        <v>0.1724622167366734</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1107257843713779</v>
+        <v>1.573003227556818e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05461671659743907</v>
+        <v>0.0001762716745704805</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08267132757374254</v>
+        <v>8.892107430795126e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1691141950517416</v>
+        <v>0.002374539614617143</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1748170833844273</v>
+        <v>0.01038304044067835</v>
       </c>
       <c r="N4" t="n">
-        <v>1.003133858011834</v>
+        <v>1.000124527936782</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1822594085453532</v>
+        <v>0.01082506796809479</v>
       </c>
       <c r="P4" t="n">
-        <v>124.9760603580155</v>
+        <v>136.2703261230999</v>
       </c>
       <c r="Q4" t="n">
-        <v>196.8897340252393</v>
+        <v>208.1839997903238</v>
       </c>
     </row>
     <row r="5">
@@ -682,52 +682,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9955882203748218</v>
+        <v>0.9998530839640217</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7370636771906115</v>
+        <v>0.7090728648069167</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9801780045208192</v>
+        <v>0.9999970770935473</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9904037450105047</v>
+        <v>0.9987693439139318</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9856858110498747</v>
+        <v>0.9998919145963243</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02950159066794386</v>
+        <v>8.72157053990017e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.758256401336822</v>
+        <v>0.1727069148484806</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1066105239286756</v>
+        <v>2.876606012049001e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05698384354352355</v>
+        <v>0.0001404983313837302</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08179718373609957</v>
+        <v>7.168749681004505e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1576589292722357</v>
+        <v>0.002270319976588255</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1717602709241688</v>
+        <v>0.009338934917805226</v>
       </c>
       <c r="N5" t="n">
-        <v>1.003025220314408</v>
+        <v>1.000100742424671</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1790724612501873</v>
+        <v>0.009736512711516562</v>
       </c>
       <c r="P5" t="n">
-        <v>125.0466221922856</v>
+        <v>136.6942522709602</v>
       </c>
       <c r="Q5" t="n">
-        <v>196.9602958595094</v>
+        <v>208.607925938184</v>
       </c>
     </row>
     <row r="6">
@@ -737,52 +737,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9957155939246108</v>
+        <v>0.9998788224804795</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7363451146979489</v>
+        <v>0.7087273327192742</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9808406835117005</v>
+        <v>0.9999933761328023</v>
       </c>
       <c r="E6" t="n">
-        <v>0.990035126130593</v>
+        <v>0.9989692560007344</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9858061498964311</v>
+        <v>0.9999063743033407</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02864984315400322</v>
+        <v>7.193621018363244e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.763061432033932</v>
+        <v>0.1729120376219141</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1030463744721492</v>
+        <v>6.518941510005522e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05917275167519273</v>
+        <v>0.0001176752901318586</v>
       </c>
       <c r="K6" t="n">
-        <v>0.08110951789791207</v>
+        <v>6.209711582093204e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1473406676624917</v>
+        <v>0.002228712559476173</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1692626454773859</v>
+        <v>0.008481521690335553</v>
       </c>
       <c r="N6" t="n">
-        <v>1.002937878451695</v>
+        <v>1.000083093156243</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1764685067173375</v>
+        <v>0.008842597627863441</v>
       </c>
       <c r="P6" t="n">
-        <v>125.1052146207825</v>
+        <v>137.0794616026462</v>
       </c>
       <c r="Q6" t="n">
-        <v>197.0188882880063</v>
+        <v>208.99313526987</v>
       </c>
     </row>
     <row r="7">
@@ -792,52 +792,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.99581785821407</v>
+        <v>0.9998976716267886</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7356893219974219</v>
+        <v>0.7084370194965579</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9814158400069852</v>
+        <v>0.9999880542767223</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9896953485837207</v>
+        <v>0.9990863052739026</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9859002716526637</v>
+        <v>0.9999124987477674</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02796600137950646</v>
+        <v>6.074654269389782e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.767446720842005</v>
+        <v>0.1730843800917968</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09995295557960175</v>
+        <v>1.17564964720958e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06119039612000668</v>
+        <v>0.0001043123142720773</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0805716673347438</v>
+        <v>5.803508639440508e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1380484898715281</v>
+        <v>0.002190104591442392</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1672303841396846</v>
+        <v>0.007794006844614509</v>
       </c>
       <c r="N7" t="n">
-        <v>1.002867754367495</v>
+        <v>1.000070168027345</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1743497278071293</v>
+        <v>0.008125813851808123</v>
       </c>
       <c r="P7" t="n">
-        <v>125.153531486071</v>
+        <v>137.4176007755032</v>
       </c>
       <c r="Q7" t="n">
-        <v>197.0672051532948</v>
+        <v>209.331274442727</v>
       </c>
     </row>
     <row r="8">
@@ -847,52 +847,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9958998847264192</v>
+        <v>0.9999112427211887</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7350916804452863</v>
+        <v>0.7081927556451891</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9819161286510374</v>
+        <v>0.9999816953767825</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9893831676413276</v>
+        <v>0.999143514182279</v>
       </c>
       <c r="F8" t="n">
-        <v>0.985973504099408</v>
+        <v>0.9999127049592959</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02741748971372988</v>
+        <v>5.269015481722135e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.771443152653022</v>
+        <v>0.1732293856656182</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09726220557342903</v>
+        <v>1.80146679507136e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.06304416824236811</v>
+        <v>9.77810369654895e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08015318690789858</v>
+        <v>5.789831687904038e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1296778676098788</v>
+        <v>0.002154261642754255</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1655822747570823</v>
+        <v>0.007258798441699655</v>
       </c>
       <c r="N8" t="n">
-        <v>1.00281150761617</v>
+        <v>1.000060862134042</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1726314549960528</v>
+        <v>0.007567820519147055</v>
       </c>
       <c r="P8" t="n">
-        <v>125.1931483170034</v>
+        <v>137.7021638709633</v>
       </c>
       <c r="Q8" t="n">
-        <v>197.1068219842272</v>
+        <v>209.6158375381872</v>
       </c>
     </row>
     <row r="9">
@@ -902,52 +902,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9959655626866977</v>
+        <v>0.9999207602084493</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7345477897842017</v>
+        <v>0.7079862848220606</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9823521776291393</v>
+        <v>0.9999747299363939</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9890969941265321</v>
+        <v>0.999157604700926</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9860300380090747</v>
+        <v>0.9999087505406208</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02697830089092839</v>
+        <v>4.704016324521163e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.775080152008081</v>
+        <v>0.1733519556653025</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09491696187367982</v>
+        <v>2.486977194500302e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06474350478680735</v>
+        <v>9.617238741615905e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.07983012881411179</v>
+        <v>6.052107968058104e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1221458804857937</v>
+        <v>0.002120835112362275</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1642507256937649</v>
+        <v>0.006858583180600176</v>
       </c>
       <c r="N9" t="n">
-        <v>1.00276647130055</v>
+        <v>1.000054335857063</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1712432191324235</v>
+        <v>0.007150567265822769</v>
       </c>
       <c r="P9" t="n">
-        <v>125.2254448136012</v>
+        <v>137.9290175680621</v>
       </c>
       <c r="Q9" t="n">
-        <v>197.139118480825</v>
+        <v>209.8426912352859</v>
       </c>
     </row>
     <row r="10">
@@ -957,52 +957,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9960180579272695</v>
+        <v>0.999927195403388</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7340533521690804</v>
+        <v>0.707811404013558</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9827329773982904</v>
+        <v>0.9999674781731164</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9888351710824794</v>
+        <v>0.9991414887582121</v>
       </c>
       <c r="F10" t="n">
-        <v>0.986073187009316</v>
+        <v>0.9999019836602382</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02662726497550647</v>
+        <v>4.321995354365868e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>1.778386458617073</v>
+        <v>0.1734557724676872</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09286887025022261</v>
+        <v>3.200666331660429e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.06629824498438651</v>
+        <v>9.801227029295102e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.07958355761730457</v>
+        <v>6.500920388001572e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1153599144599797</v>
+        <v>0.002089834010023625</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1631786290404061</v>
+        <v>0.006574188432320652</v>
       </c>
       <c r="N10" t="n">
-        <v>1.002730474564158</v>
+        <v>1.000049923151962</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1701254811049852</v>
+        <v>0.006854065244330699</v>
       </c>
       <c r="P10" t="n">
-        <v>125.2516391781363</v>
+        <v>138.0984165635335</v>
       </c>
       <c r="Q10" t="n">
-        <v>197.1653128453601</v>
+        <v>210.0120902307573</v>
       </c>
     </row>
     <row r="11">
@@ -1012,52 +1012,52 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9960599507222522</v>
+        <v>0.9999312771372452</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7336043855640033</v>
+        <v>0.707662971762218</v>
       </c>
       <c r="D11" t="n">
-        <v>0.983066236345346</v>
+        <v>0.9999601555699411</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9885961875577304</v>
+        <v>0.9991041580098815</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9861058484770966</v>
+        <v>0.9998933375705696</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02634712766255844</v>
+        <v>4.079686000433246e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>1.781388700372524</v>
+        <v>0.173543888264022</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09107647195274368</v>
+        <v>3.921327244322826e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.06771736106651305</v>
+        <v>0.0001022741497157398</v>
       </c>
       <c r="K11" t="n">
-        <v>0.07939691650962837</v>
+        <v>7.074371107948401e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1092499049905258</v>
+        <v>0.002061186047406181</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1623179831767215</v>
+        <v>0.006387241971644136</v>
       </c>
       <c r="N11" t="n">
-        <v>1.00270174807617</v>
+        <v>1.000047124248746</v>
       </c>
       <c r="O11" t="n">
-        <v>0.169228195765101</v>
+        <v>0.006659160085790659</v>
       </c>
       <c r="P11" t="n">
-        <v>125.2727920341</v>
+        <v>138.2138108803878</v>
       </c>
       <c r="Q11" t="n">
-        <v>197.1864657013238</v>
+        <v>210.1274845476117</v>
       </c>
     </row>
     <row r="12">
@@ -1067,52 +1067,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9960933066867576</v>
+        <v>0.9999336186695397</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7331971051169062</v>
+        <v>0.7075371517372739</v>
       </c>
       <c r="D12" t="n">
-        <v>0.983358451826574</v>
+        <v>0.9999529684591885</v>
       </c>
       <c r="E12" t="n">
-        <v>0.98837834187276</v>
+        <v>0.999053391649969</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9861301760231791</v>
+        <v>0.9998836361402291</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02612407617432098</v>
+        <v>3.940682528542342e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>1.784112186597618</v>
+        <v>0.1736185804659708</v>
       </c>
       <c r="I12" t="n">
-        <v>0.089504821631942</v>
+        <v>4.628653542136886e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.06901095783343626</v>
+        <v>0.0001080699109677178</v>
       </c>
       <c r="K12" t="n">
-        <v>0.07925789887029867</v>
+        <v>7.717817154255848e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.10375127876696</v>
+        <v>0.002034533833808637</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1616294409268342</v>
+        <v>0.006277485586237807</v>
       </c>
       <c r="N12" t="n">
-        <v>1.002678875414795</v>
+        <v>1.000045518626601</v>
       </c>
       <c r="O12" t="n">
-        <v>0.168510340846157</v>
+        <v>0.006544731143830544</v>
       </c>
       <c r="P12" t="n">
-        <v>125.2897958621418</v>
+        <v>138.2831430521371</v>
       </c>
       <c r="Q12" t="n">
-        <v>197.2034695293656</v>
+        <v>210.196816719361</v>
       </c>
     </row>
     <row r="13">
@@ -1122,52 +1122,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9961197919017702</v>
+        <v>0.9999346385812635</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7328279172045631</v>
+        <v>0.7074298321839678</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9836151269643677</v>
+        <v>0.9999460044571322</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9881800237612184</v>
+        <v>0.9989936219940579</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9861479299769944</v>
+        <v>0.9998733251239676</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0259469694195779</v>
+        <v>3.880136162821303e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>1.78658094786741</v>
+        <v>0.1736822899887767</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08812432132114362</v>
+        <v>5.314022386723182e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.07018859726176575</v>
+        <v>0.0001148935370139727</v>
       </c>
       <c r="K13" t="n">
-        <v>0.07915644545038542</v>
+        <v>8.401693903767449e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09879811149020812</v>
+        <v>0.002032106089832827</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1610806301812167</v>
+        <v>0.006229073898117844</v>
       </c>
       <c r="N13" t="n">
-        <v>1.0026607141245</v>
+        <v>1.000044819258562</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1679381660909038</v>
+        <v>0.006494258469921305</v>
       </c>
       <c r="P13" t="n">
-        <v>125.3034009231258</v>
+        <v>138.3141104368803</v>
       </c>
       <c r="Q13" t="n">
-        <v>197.2170745903496</v>
+        <v>210.2277841041042</v>
       </c>
     </row>
     <row r="14">
@@ -1177,52 +1177,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.996140791812143</v>
+        <v>0.9999347060752406</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7324935287087418</v>
+        <v>0.7073384769350358</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9838411596076533</v>
+        <v>0.9999393570146637</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9879997748658138</v>
+        <v>0.9989292177065399</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9861606422045334</v>
+        <v>0.9998628504969761</v>
       </c>
       <c r="G14" t="n">
-        <v>0.02580654292221991</v>
+        <v>3.876129428785792e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>1.788817005278683</v>
+        <v>0.173736522410884</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0869086284535423</v>
+        <v>5.968236720278836e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.07125893927183864</v>
+        <v>0.0001222462775827547</v>
       </c>
       <c r="K14" t="n">
-        <v>0.07908380253535072</v>
+        <v>9.096422112668872e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.09433942106379227</v>
+        <v>0.002056344026645735</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1606441499782046</v>
+        <v>0.006225856911932519</v>
       </c>
       <c r="N14" t="n">
-        <v>1.002646314185959</v>
+        <v>1.000044772976978</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1674831040220109</v>
+        <v>0.006490904529973991</v>
       </c>
       <c r="P14" t="n">
-        <v>125.3142544351392</v>
+        <v>138.3161767582793</v>
       </c>
       <c r="Q14" t="n">
-        <v>197.227928102363</v>
+        <v>210.2298504255031</v>
       </c>
     </row>
     <row r="15">
@@ -1232,52 +1232,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9961573393972195</v>
+        <v>0.9999340739850815</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7321908668843878</v>
+        <v>0.7072599407577053</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9840401993975757</v>
+        <v>0.9999330582506817</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9878360428634753</v>
+        <v>0.9988625588690442</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9861692706198303</v>
+        <v>0.9998524402580747</v>
       </c>
       <c r="G15" t="n">
-        <v>0.02569588914461835</v>
+        <v>3.913653031115721e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>1.790840906291768</v>
+        <v>0.1737831448783337</v>
       </c>
       <c r="I15" t="n">
-        <v>0.08583811381698289</v>
+        <v>6.588135531016111e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.07223120176533633</v>
+        <v>0.0001298564097278247</v>
       </c>
       <c r="K15" t="n">
-        <v>0.07903449620902964</v>
+        <v>9.786879790262405e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09032241950351133</v>
+        <v>0.002077746225470995</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1602993735003925</v>
+        <v>0.006255919621539044</v>
       </c>
       <c r="N15" t="n">
-        <v>1.002634967270478</v>
+        <v>1.00004520641023</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1671236496957526</v>
+        <v>0.006522247071366853</v>
       </c>
       <c r="P15" t="n">
-        <v>125.322848510675</v>
+        <v>138.2969084961645</v>
       </c>
       <c r="Q15" t="n">
-        <v>197.2365221778989</v>
+        <v>210.2105821633884</v>
       </c>
     </row>
     <row r="16">
@@ -1287,52 +1287,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9961703748000784</v>
+        <v>0.9999329607819376</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7319170373919179</v>
+        <v>0.7071925056725912</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9842161103529705</v>
+        <v>0.9999271554049594</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9876875552605607</v>
+        <v>0.9987959531365763</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9861748754168705</v>
+        <v>0.9998423280630814</v>
       </c>
       <c r="G16" t="n">
-        <v>0.02560872134567802</v>
+        <v>3.979737578525357e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>1.792672005368783</v>
+        <v>0.1738231772579014</v>
       </c>
       <c r="I16" t="n">
-        <v>0.08489199519138131</v>
+        <v>7.169069672019093e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.07311294097942543</v>
+        <v>0.0001374604791167152</v>
       </c>
       <c r="K16" t="n">
-        <v>0.07900246808540337</v>
+        <v>0.0001045756974623587</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08671244930398551</v>
+        <v>0.002096477614408582</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1600272518844151</v>
+        <v>0.006308516131805764</v>
       </c>
       <c r="N16" t="n">
-        <v>1.002626028708518</v>
+        <v>1.000045969749529</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1668399432992136</v>
+        <v>0.006577082723965414</v>
       </c>
       <c r="P16" t="n">
-        <v>125.329644615897</v>
+        <v>138.2634191657831</v>
       </c>
       <c r="Q16" t="n">
-        <v>197.2433182831208</v>
+        <v>210.177092833007</v>
       </c>
     </row>
     <row r="17">
@@ -1342,52 +1342,52 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9961805795736597</v>
+        <v>0.9999315140285157</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7316693951982278</v>
+        <v>0.7071347142826598</v>
       </c>
       <c r="D17" t="n">
-        <v>0.984371646548576</v>
+        <v>0.9999216394538921</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9875529404735318</v>
+        <v>0.9987306049811738</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9861781281164559</v>
+        <v>0.9998326116059646</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0255404819777514</v>
+        <v>4.065623111301807e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>1.794327989858276</v>
+        <v>0.1738574847234227</v>
       </c>
       <c r="I17" t="n">
-        <v>0.08405546007458228</v>
+        <v>7.711927209856813e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07391230156030779</v>
+        <v>0.0001449209767301462</v>
       </c>
       <c r="K17" t="n">
-        <v>0.07898388081744503</v>
+        <v>0.0001110201244143572</v>
       </c>
       <c r="L17" t="n">
-        <v>0.08346066443578745</v>
+        <v>0.002113014470438722</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1598138979493066</v>
+        <v>0.006376223891381016</v>
       </c>
       <c r="N17" t="n">
-        <v>1.00261903114949</v>
+        <v>1.000046961809018</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1666175064453841</v>
+        <v>0.006647672943040169</v>
       </c>
       <c r="P17" t="n">
-        <v>125.3349811141397</v>
+        <v>138.2207168936092</v>
       </c>
       <c r="Q17" t="n">
-        <v>197.2486547813635</v>
+        <v>210.134390560833</v>
       </c>
     </row>
     <row r="18">
@@ -1397,52 +1397,52 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9961885207662464</v>
+        <v>0.9999298566774968</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7314456155698581</v>
+        <v>0.7070846475444093</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9845093022281817</v>
+        <v>0.9999165177577981</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9874310507140796</v>
+        <v>0.9986675355019857</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9861795723499096</v>
+        <v>0.9998233841562947</v>
       </c>
       <c r="G18" t="n">
-        <v>0.02548737918635817</v>
+        <v>4.164010627165804e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>1.795824405263596</v>
+        <v>0.1738872065020187</v>
       </c>
       <c r="I18" t="n">
-        <v>0.08331509343793683</v>
+        <v>8.215983771862721e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.07463609922823003</v>
+        <v>0.0001521213283860454</v>
       </c>
       <c r="K18" t="n">
-        <v>0.07897562787139407</v>
+        <v>0.0001171402178431089</v>
       </c>
       <c r="L18" t="n">
-        <v>0.08052995538236898</v>
+        <v>0.002127667062268657</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1596476720355113</v>
+        <v>0.006452914556358083</v>
       </c>
       <c r="N18" t="n">
-        <v>1.002613585760288</v>
+        <v>1.000048098278288</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1664442039503033</v>
+        <v>0.006727628488396871</v>
       </c>
       <c r="P18" t="n">
-        <v>125.3391437664125</v>
+        <v>138.1728935241352</v>
       </c>
       <c r="Q18" t="n">
-        <v>197.2528174336364</v>
+        <v>210.086567191359</v>
       </c>
     </row>
     <row r="19">
@@ -1452,52 +1452,52 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9961946623900182</v>
+        <v>0.9999280832059825</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7312434782998367</v>
+        <v>0.7070413135284663</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9846313437862548</v>
+        <v>0.9999117881763701</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9873207106326835</v>
+        <v>0.9986074544069113</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9861796860377421</v>
+        <v>0.9998147033618624</v>
       </c>
       <c r="G19" t="n">
-        <v>0.02544631011991668</v>
+        <v>4.26929155725568e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>1.797176098118985</v>
+        <v>0.1739129314458144</v>
       </c>
       <c r="I19" t="n">
-        <v>0.08265870571648316</v>
+        <v>8.681449998405561e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.07529131336559336</v>
+        <v>0.0001589805100056863</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0789749782121956</v>
+        <v>0.0001228977429298284</v>
       </c>
       <c r="L19" t="n">
-        <v>0.07789527198193398</v>
+        <v>0.002140568373140222</v>
       </c>
       <c r="M19" t="n">
-        <v>0.15951899610992</v>
+        <v>0.006533981601792034</v>
       </c>
       <c r="N19" t="n">
-        <v>1.00260937436113</v>
+        <v>1.000049314373041</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1663100500241638</v>
+        <v>0.006812146725786864</v>
       </c>
       <c r="P19" t="n">
-        <v>125.342369063924</v>
+        <v>138.1229551262886</v>
       </c>
       <c r="Q19" t="n">
-        <v>197.2560427311478</v>
+        <v>210.0366287935124</v>
       </c>
     </row>
     <row r="20">
@@ -1507,52 +1507,52 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9961993829218925</v>
+        <v>0.9999262596545615</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7310609340654546</v>
+        <v>0.7070037405018341</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9847397346659048</v>
+        <v>0.9999074351362129</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9872209051256436</v>
+        <v>0.9985506973668342</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9861788520120145</v>
+        <v>0.9998065894693512</v>
       </c>
       <c r="G20" t="n">
-        <v>0.02541474390153781</v>
+        <v>4.377545446933393e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>1.798396772254837</v>
+        <v>0.1739352364174935</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08207573673736537</v>
+        <v>9.109858559860901e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.07588397179371568</v>
+        <v>0.0001654601995919086</v>
       </c>
       <c r="K20" t="n">
-        <v>0.07897974417944077</v>
+        <v>0.0001282792710893661</v>
       </c>
       <c r="L20" t="n">
-        <v>0.07552092102102674</v>
+        <v>0.002152065520563673</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1594200235275914</v>
+        <v>0.006616302174880915</v>
       </c>
       <c r="N20" t="n">
-        <v>1.002606137424988</v>
+        <v>1.000050564808301</v>
       </c>
       <c r="O20" t="n">
-        <v>0.166206863974104</v>
+        <v>0.006897971856099217</v>
       </c>
       <c r="P20" t="n">
-        <v>125.3448516095998</v>
+        <v>138.0728745958166</v>
       </c>
       <c r="Q20" t="n">
-        <v>197.2585252768236</v>
+        <v>209.9865482630404</v>
       </c>
     </row>
     <row r="21">
@@ -1562,52 +1562,52 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9962029716541286</v>
+        <v>0.9999244294517765</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7308961247173502</v>
+        <v>0.7069708951282507</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9848361497982783</v>
+        <v>0.9999034325047158</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9871306041725312</v>
+        <v>0.9984973874046208</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9861772912174728</v>
+        <v>0.9997990315019074</v>
       </c>
       <c r="G21" t="n">
-        <v>0.02539074603255005</v>
+        <v>4.486194190314459e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>1.799498853124488</v>
+        <v>0.1739547348500989</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08155717805906335</v>
+        <v>9.503781321847835e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.07642019091144686</v>
+        <v>0.0001715463521912489</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0789886632036588</v>
+        <v>0.0001332920827048637</v>
       </c>
       <c r="L21" t="n">
-        <v>0.07338424699881439</v>
+        <v>0.002162179947893532</v>
       </c>
       <c r="M21" t="n">
-        <v>0.159344739582297</v>
+        <v>0.006697905784881167</v>
       </c>
       <c r="N21" t="n">
-        <v>1.002603676580026</v>
+        <v>1.000051819804496</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1661283750353991</v>
+        <v>0.006983049500719939</v>
       </c>
       <c r="P21" t="n">
-        <v>125.3467410015378</v>
+        <v>138.0238414834638</v>
       </c>
       <c r="Q21" t="n">
-        <v>197.2604146687616</v>
+        <v>209.9375151506876</v>
       </c>
     </row>
     <row r="22">
@@ -1617,52 +1617,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9962056615113759</v>
+        <v>0.9999226373455882</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7307473947107079</v>
+        <v>0.706942459430014</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9849218824125345</v>
+        <v>0.9998997617074283</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9870490167211928</v>
+        <v>0.9984478244007421</v>
       </c>
       <c r="F22" t="n">
-        <v>0.986175242374485</v>
+        <v>0.9997920416032338</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0253727589447518</v>
+        <v>4.59258135515361e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>1.800493411363744</v>
+        <v>0.1739716155089304</v>
       </c>
       <c r="I22" t="n">
-        <v>0.08109607418416666</v>
+        <v>9.865046306451757e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.07690466809210417</v>
+        <v>0.0001772047318329287</v>
       </c>
       <c r="K22" t="n">
-        <v>0.07900037113813542</v>
+        <v>0.0001379281234821933</v>
       </c>
       <c r="L22" t="n">
-        <v>0.07146297095756043</v>
+        <v>0.002171224164873523</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1592882887871918</v>
+        <v>0.006776858678734277</v>
       </c>
       <c r="N22" t="n">
-        <v>1.002601832106485</v>
+        <v>1.000053048677311</v>
       </c>
       <c r="O22" t="n">
-        <v>0.166069521013077</v>
+        <v>0.007065363582719399</v>
       </c>
       <c r="P22" t="n">
-        <v>125.3481583259372</v>
+        <v>137.9769664244685</v>
       </c>
       <c r="Q22" t="n">
-        <v>197.2618319931611</v>
+        <v>209.8906400916923</v>
       </c>
     </row>
     <row r="23">
@@ -1672,52 +1672,52 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9962076725387689</v>
+        <v>0.9999209056972108</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7306132078315807</v>
+        <v>0.7069175751231309</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9849983378848244</v>
+        <v>0.9998964157736702</v>
       </c>
       <c r="E23" t="n">
-        <v>0.986975390672811</v>
+        <v>0.9984017740431137</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9861729383354566</v>
+        <v>0.9997855956000572</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02535931119531526</v>
+        <v>4.695379483162124e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>1.801390719642342</v>
+        <v>0.1739863879084423</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0806848664444315</v>
+        <v>0.0001019433953976204</v>
       </c>
       <c r="J23" t="n">
-        <v>0.07734186939889609</v>
+        <v>0.0001824620888473386</v>
       </c>
       <c r="K23" t="n">
-        <v>0.07901353736811846</v>
+        <v>0.0001422034263116366</v>
       </c>
       <c r="L23" t="n">
-        <v>0.06972960555214458</v>
+        <v>0.002179166116691342</v>
       </c>
       <c r="M23" t="n">
-        <v>0.159246071208414</v>
+        <v>0.006852283913529943</v>
       </c>
       <c r="N23" t="n">
-        <v>1.002600453116273</v>
+        <v>1.000054236093341</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1660255061445682</v>
+        <v>0.007143999825912076</v>
       </c>
       <c r="P23" t="n">
-        <v>125.3492186217</v>
+        <v>137.9326930569835</v>
       </c>
       <c r="Q23" t="n">
-        <v>197.2628922889238</v>
+        <v>209.8463667242073</v>
       </c>
     </row>
     <row r="24">
@@ -1727,52 +1727,52 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9962091093878578</v>
+        <v>0.9999192544317519</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7304922277284074</v>
+        <v>0.7068956744013415</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9850663957436541</v>
+        <v>0.9998933675840456</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9869088714659419</v>
+        <v>0.9983593129724532</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9861704359420683</v>
+        <v>0.9997796806833367</v>
       </c>
       <c r="G24" t="n">
-        <v>0.02534970297884091</v>
+        <v>4.793405733901431e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>1.802199714149324</v>
+        <v>0.1739993891229584</v>
       </c>
       <c r="I24" t="n">
-        <v>0.08031882438802418</v>
+        <v>0.0001049433000275196</v>
       </c>
       <c r="J24" t="n">
-        <v>0.07773686933178921</v>
+        <v>0.0001873096735170972</v>
       </c>
       <c r="K24" t="n">
-        <v>0.07902783707678329</v>
+        <v>0.0001461264867723084</v>
       </c>
       <c r="L24" t="n">
-        <v>0.06817379018756561</v>
+        <v>0.002186343323073737</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1592159005214018</v>
+        <v>0.006923442593032336</v>
       </c>
       <c r="N24" t="n">
-        <v>1.002599467848326</v>
+        <v>1.000055368389656</v>
       </c>
       <c r="O24" t="n">
-        <v>0.165994051028948</v>
+        <v>0.007218187877719659</v>
       </c>
       <c r="P24" t="n">
-        <v>125.3499765316492</v>
+        <v>137.8913685940589</v>
       </c>
       <c r="Q24" t="n">
-        <v>197.263650198873</v>
+        <v>209.8050422612827</v>
       </c>
     </row>
     <row r="25">
@@ -1782,52 +1782,52 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9962101187704762</v>
+        <v>0.9999176856292845</v>
       </c>
       <c r="C25" t="n">
-        <v>0.730383047936787</v>
+        <v>0.7068764138177097</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9851271834158597</v>
+        <v>0.9998905858292017</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9868487589088375</v>
+        <v>0.9983201063556353</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9861678061482856</v>
+        <v>0.9997742415869321</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0253429532326242</v>
+        <v>4.886536625236433e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>1.802929799918616</v>
+        <v>0.1740108230374161</v>
       </c>
       <c r="I25" t="n">
-        <v>0.07999188426794122</v>
+        <v>0.0001076809903496744</v>
       </c>
       <c r="J25" t="n">
-        <v>0.07809382572287946</v>
+        <v>0.0001917857121963587</v>
       </c>
       <c r="K25" t="n">
-        <v>0.07904286480388589</v>
+        <v>0.0001497339600562937</v>
       </c>
       <c r="L25" t="n">
-        <v>0.06677235497048759</v>
+        <v>0.002192587007806552</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1591947022756229</v>
+        <v>0.006990376688874808</v>
       </c>
       <c r="N25" t="n">
-        <v>1.002598775700245</v>
+        <v>1.000056444139919</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1659719503299598</v>
+        <v>0.007287971496594826</v>
       </c>
       <c r="P25" t="n">
-        <v>125.3505091331549</v>
+        <v>137.852883338027</v>
       </c>
       <c r="Q25" t="n">
-        <v>197.2641828003787</v>
+        <v>209.7665570052509</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9962107981948848</v>
+        <v>0.9999162161227563</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7302846722104392</v>
+        <v>0.7068595236204442</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9851814286709981</v>
+        <v>0.9998880610333211</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9867945575244697</v>
+        <v>0.9982842269151518</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9861651818328554</v>
+        <v>0.9997692815236056</v>
       </c>
       <c r="G26" t="n">
-        <v>0.02533840991847569</v>
+        <v>4.973772880691787e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>1.803587638853682</v>
+        <v>0.1740208497881315</v>
       </c>
       <c r="I26" t="n">
-        <v>0.07970013185194311</v>
+        <v>0.0001101657920794041</v>
       </c>
       <c r="J26" t="n">
-        <v>0.07841568078092492</v>
+        <v>0.0001958819024935358</v>
       </c>
       <c r="K26" t="n">
-        <v>0.07905786122542077</v>
+        <v>0.0001530237153036247</v>
       </c>
       <c r="L26" t="n">
-        <v>0.06550924624310883</v>
+        <v>0.002198212784960268</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1591804319584405</v>
+        <v>0.007052498054371789</v>
       </c>
       <c r="N26" t="n">
-        <v>1.002598309809222</v>
+        <v>1.000057451801539</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1659570724958314</v>
+        <v>0.007352737497229967</v>
       </c>
       <c r="P26" t="n">
-        <v>125.3508677118417</v>
+        <v>137.8174935638638</v>
       </c>
       <c r="Q26" t="n">
-        <v>197.2645413790655</v>
+        <v>209.7311672310877</v>
       </c>
     </row>
   </sheetData>

--- a/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_23_8.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_23_8.xlsx
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_1</t>
+          <t>model_23_8_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9997732507292887</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7099302795942648</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9999966257932638</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9980198515449996</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9998270790293392</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0001346081621526972</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1721979163923205</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I2" t="n">
-        <v>3.320757451707956e-06</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0002260644195962692</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000114689598327516</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002490921722587949</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01160207576913275</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000155485214202</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0120960001542325</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P2" t="n">
-        <v>135.8262850050551</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q2" t="n">
-        <v>207.739958672279</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_0</t>
+          <t>model_23_8_22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9997729042618807</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7099189256082213</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9999966746640441</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E3" t="n">
-        <v>0.998020929730955</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9998272013208217</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0001348138401726944</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1722046566089026</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I3" t="n">
-        <v>3.272660811314534e-06</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002259413280767414</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0001146084886682967</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002484036603077944</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01161093623153165</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000155722791853</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01210523782485941</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P3" t="n">
-        <v>135.8232313857044</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q3" t="n">
-        <v>207.7369050529283</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_2</t>
+          <t>model_23_8_21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9998183967588591</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7094850620875969</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9999984016784834</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9984559972565147</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9998659310111313</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000107807528792762</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1724622167366734</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I4" t="n">
-        <v>1.573003227556818e-06</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0001762716745704805</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>8.892107430795126e-05</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002374539614617143</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01038304044067835</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000124527936782</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01082506796809479</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P4" t="n">
-        <v>136.2703261230999</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q4" t="n">
-        <v>208.1839997903238</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_3</t>
+          <t>model_23_8_20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9998530839640217</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7090728648069167</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9999970770935473</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9987693439139318</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9998919145963243</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G5" t="n">
-        <v>8.72157053990017e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1727069148484806</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I5" t="n">
-        <v>2.876606012049001e-06</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001404983313837302</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>7.168749681004505e-05</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002270319976588255</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M5" t="n">
-        <v>0.009338934917805226</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000100742424671</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O5" t="n">
-        <v>0.009736512711516562</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P5" t="n">
-        <v>136.6942522709602</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q5" t="n">
-        <v>208.607925938184</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_4</t>
+          <t>model_23_8_19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9998788224804795</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7087273327192742</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9999933761328023</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9989692560007344</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9999063743033407</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G6" t="n">
-        <v>7.193621018363244e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1729120376219141</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I6" t="n">
-        <v>6.518941510005522e-06</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001176752901318586</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>6.209711582093204e-05</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002228712559476173</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M6" t="n">
-        <v>0.008481521690335553</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000083093156243</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O6" t="n">
-        <v>0.008842597627863441</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P6" t="n">
-        <v>137.0794616026462</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q6" t="n">
-        <v>208.99313526987</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_5</t>
+          <t>model_23_8_18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9998976716267886</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7084370194965579</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9999880542767223</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9990863052739026</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9999124987477674</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G7" t="n">
-        <v>6.074654269389782e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1730843800917968</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I7" t="n">
-        <v>1.17564964720958e-05</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001043123142720773</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>5.803508639440508e-05</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002190104591442392</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M7" t="n">
-        <v>0.007794006844614509</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000070168027345</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008125813851808123</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P7" t="n">
-        <v>137.4176007755032</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q7" t="n">
-        <v>209.331274442727</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_6</t>
+          <t>model_23_8_17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9999112427211887</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7081927556451891</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9999816953767825</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E8" t="n">
-        <v>0.999143514182279</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9999127049592959</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G8" t="n">
-        <v>5.269015481722135e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1732293856656182</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I8" t="n">
-        <v>1.80146679507136e-05</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>9.77810369654895e-05</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.789831687904038e-05</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002154261642754255</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M8" t="n">
-        <v>0.007258798441699655</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000060862134042</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O8" t="n">
-        <v>0.007567820519147055</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P8" t="n">
-        <v>137.7021638709633</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q8" t="n">
-        <v>209.6158375381872</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_7</t>
+          <t>model_23_8_16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9999207602084493</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7079862848220606</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9999747299363939</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E9" t="n">
-        <v>0.999157604700926</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9999087505406208</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G9" t="n">
-        <v>4.704016324521163e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1733519556653025</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I9" t="n">
-        <v>2.486977194500302e-05</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>9.617238741615905e-05</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>6.052107968058104e-05</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002120835112362275</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M9" t="n">
-        <v>0.006858583180600176</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000054335857063</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O9" t="n">
-        <v>0.007150567265822769</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P9" t="n">
-        <v>137.9290175680621</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q9" t="n">
-        <v>209.8426912352859</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_8</t>
+          <t>model_23_8_15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.999927195403388</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C10" t="n">
-        <v>0.707811404013558</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9999674781731164</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9991414887582121</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9999019836602382</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G10" t="n">
-        <v>4.321995354365868e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1734557724676872</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I10" t="n">
-        <v>3.200666331660429e-05</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>9.801227029295102e-05</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>6.500920388001572e-05</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.002089834010023625</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M10" t="n">
-        <v>0.006574188432320652</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000049923151962</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O10" t="n">
-        <v>0.006854065244330699</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P10" t="n">
-        <v>138.0984165635335</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q10" t="n">
-        <v>210.0120902307573</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_9</t>
+          <t>model_23_8_14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9999312771372452</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C11" t="n">
-        <v>0.707662971762218</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9999601555699411</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9991041580098815</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9998933375705696</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G11" t="n">
-        <v>4.079686000433246e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H11" t="n">
-        <v>0.173543888264022</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I11" t="n">
-        <v>3.921327244322826e-05</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001022741497157398</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>7.074371107948401e-05</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002061186047406181</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M11" t="n">
-        <v>0.006387241971644136</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000047124248746</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O11" t="n">
-        <v>0.006659160085790659</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P11" t="n">
-        <v>138.2138108803878</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q11" t="n">
-        <v>210.1274845476117</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_10</t>
+          <t>model_23_8_13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9999336186695397</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7075371517372739</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9999529684591885</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E12" t="n">
-        <v>0.999053391649969</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9998836361402291</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G12" t="n">
-        <v>3.940682528542342e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1736185804659708</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I12" t="n">
-        <v>4.628653542136886e-05</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0001080699109677178</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>7.717817154255848e-05</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002034533833808637</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M12" t="n">
-        <v>0.006277485586237807</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000045518626601</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O12" t="n">
-        <v>0.006544731143830544</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P12" t="n">
-        <v>138.2831430521371</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q12" t="n">
-        <v>210.196816719361</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_11</t>
+          <t>model_23_8_23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9999346385812635</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7074298321839678</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9999460044571322</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9989936219940579</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9998733251239676</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G13" t="n">
-        <v>3.880136162821303e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1736822899887767</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I13" t="n">
-        <v>5.314022386723182e-05</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0001148935370139727</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>8.401693903767449e-05</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.002032106089832827</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M13" t="n">
-        <v>0.006229073898117844</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000044819258562</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O13" t="n">
-        <v>0.006494258469921305</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P13" t="n">
-        <v>138.3141104368803</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q13" t="n">
-        <v>210.2277841041042</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="14">
@@ -1177,657 +1177,657 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9999347060752406</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7073384769350358</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9999393570146637</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9989292177065399</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9998628504969761</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G14" t="n">
-        <v>3.876129428785792e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H14" t="n">
-        <v>0.173736522410884</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I14" t="n">
-        <v>5.968236720278836e-05</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0001222462775827547</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>9.096422112668872e-05</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.002056344026645735</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M14" t="n">
-        <v>0.006225856911932519</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000044772976978</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O14" t="n">
-        <v>0.006490904529973991</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P14" t="n">
-        <v>138.3161767582793</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q14" t="n">
-        <v>210.2298504255031</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_13</t>
+          <t>model_23_8_10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9999340739850815</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7072599407577053</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9999330582506817</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9988625588690442</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9998524402580747</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G15" t="n">
-        <v>3.913653031115721e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1737831448783337</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I15" t="n">
-        <v>6.588135531016111e-05</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0001298564097278247</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>9.786879790262405e-05</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.002077746225470995</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M15" t="n">
-        <v>0.006255919621539044</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N15" t="n">
-        <v>1.00004520641023</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O15" t="n">
-        <v>0.006522247071366853</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P15" t="n">
-        <v>138.2969084961645</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q15" t="n">
-        <v>210.2105821633884</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_14</t>
+          <t>model_23_8_9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9999329607819376</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7071925056725912</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9999271554049594</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9987959531365763</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9998423280630814</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G16" t="n">
-        <v>3.979737578525357e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1738231772579014</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I16" t="n">
-        <v>7.169069672019093e-05</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0001374604791167152</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0001045756974623587</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.002096477614408582</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M16" t="n">
-        <v>0.006308516131805764</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000045969749529</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O16" t="n">
-        <v>0.006577082723965414</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P16" t="n">
-        <v>138.2634191657831</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q16" t="n">
-        <v>210.177092833007</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_15</t>
+          <t>model_23_8_8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9999315140285157</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7071347142826598</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9999216394538921</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9987306049811738</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9998326116059646</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G17" t="n">
-        <v>4.065623111301807e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1738574847234227</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I17" t="n">
-        <v>7.711927209856813e-05</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0001449209767301462</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0001110201244143572</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>0.002113014470438722</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M17" t="n">
-        <v>0.006376223891381016</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000046961809018</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O17" t="n">
-        <v>0.006647672943040169</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P17" t="n">
-        <v>138.2207168936092</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q17" t="n">
-        <v>210.134390560833</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_16</t>
+          <t>model_23_8_7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9999298566774968</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7070846475444093</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9999165177577981</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9986675355019857</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9998233841562947</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G18" t="n">
-        <v>4.164010627165804e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1738872065020187</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I18" t="n">
-        <v>8.215983771862721e-05</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0001521213283860454</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0001171402178431089</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.002127667062268657</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M18" t="n">
-        <v>0.006452914556358083</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000048098278288</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O18" t="n">
-        <v>0.006727628488396871</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P18" t="n">
-        <v>138.1728935241352</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q18" t="n">
-        <v>210.086567191359</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_17</t>
+          <t>model_23_8_6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9999280832059825</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7070413135284663</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9999117881763701</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9986074544069113</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9998147033618624</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G19" t="n">
-        <v>4.26929155725568e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1739129314458144</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I19" t="n">
-        <v>8.681449998405561e-05</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0001589805100056863</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0001228977429298284</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>0.002140568373140222</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M19" t="n">
-        <v>0.006533981601792034</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000049314373041</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O19" t="n">
-        <v>0.006812146725786864</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P19" t="n">
-        <v>138.1229551262886</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q19" t="n">
-        <v>210.0366287935124</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_18</t>
+          <t>model_23_8_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9999262596545615</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7070037405018341</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9999074351362129</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9985506973668342</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9998065894693512</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G20" t="n">
-        <v>4.377545446933393e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1739352364174935</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I20" t="n">
-        <v>9.109858559860901e-05</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0001654601995919086</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0001282792710893661</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.002152065520563673</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M20" t="n">
-        <v>0.006616302174880915</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000050564808301</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O20" t="n">
-        <v>0.006897971856099217</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P20" t="n">
-        <v>138.0728745958166</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q20" t="n">
-        <v>209.9865482630404</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_19</t>
+          <t>model_23_8_4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9999244294517765</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7069708951282507</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9999034325047158</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9984973874046208</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9997990315019074</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G21" t="n">
-        <v>4.486194190314459e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1739547348500989</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I21" t="n">
-        <v>9.503781321847835e-05</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0001715463521912489</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0001332920827048637</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0.002162179947893532</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M21" t="n">
-        <v>0.006697905784881167</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000051819804496</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O21" t="n">
-        <v>0.006983049500719939</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P21" t="n">
-        <v>138.0238414834638</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q21" t="n">
-        <v>209.9375151506876</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_20</t>
+          <t>model_23_8_3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9999226373455882</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C22" t="n">
-        <v>0.706942459430014</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9998997617074283</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9984478244007421</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9997920416032338</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G22" t="n">
-        <v>4.59258135515361e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1739716155089304</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I22" t="n">
-        <v>9.865046306451757e-05</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0001772047318329287</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0001379281234821933</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.002171224164873523</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M22" t="n">
-        <v>0.006776858678734277</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000053048677311</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O22" t="n">
-        <v>0.007065363582719399</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P22" t="n">
-        <v>137.9769664244685</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q22" t="n">
-        <v>209.8906400916923</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_21</t>
+          <t>model_23_8_2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9999209056972108</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7069175751231309</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9998964157736702</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9984017740431137</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9997855956000572</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G23" t="n">
-        <v>4.695379483162124e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1739863879084423</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0001019433953976204</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0001824620888473386</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0001422034263116366</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.002179166116691342</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M23" t="n">
-        <v>0.006852283913529943</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000054236093341</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O23" t="n">
-        <v>0.007143999825912076</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P23" t="n">
-        <v>137.9326930569835</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q23" t="n">
-        <v>209.8463667242073</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_22</t>
+          <t>model_23_8_1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9999192544317519</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7068956744013415</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9998933675840456</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9983593129724532</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9997796806833367</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G24" t="n">
-        <v>4.793405733901431e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1739993891229584</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0001049433000275196</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0001873096735170972</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0001461264867723084</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.002186343323073737</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M24" t="n">
-        <v>0.006923442593032336</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000055368389656</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O24" t="n">
-        <v>0.007218187877719659</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P24" t="n">
-        <v>137.8913685940589</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q24" t="n">
-        <v>209.8050422612827</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_23</t>
+          <t>model_23_8_11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9999176856292845</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7068764138177097</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9998905858292017</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9983201063556353</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9997742415869321</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G25" t="n">
-        <v>4.886536625236433e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1740108230374161</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0001076809903496744</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0001917857121963587</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0001497339600562937</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.002192587007806552</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M25" t="n">
-        <v>0.006990376688874808</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000056444139919</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O25" t="n">
-        <v>0.007287971496594826</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P25" t="n">
-        <v>137.852883338027</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q25" t="n">
-        <v>209.7665570052509</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9999162161227563</v>
+        <v>0.9998202048173259</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7068595236204442</v>
+        <v>0.662549110391359</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9998880610333211</v>
+        <v>0.9998108687614812</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9982842269151518</v>
+        <v>0.9998886915928439</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9997692815236056</v>
+        <v>0.9998885464154755</v>
       </c>
       <c r="G26" t="n">
-        <v>4.973772880691787e-05</v>
+        <v>0.0001067341871827888</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1740208497881315</v>
+        <v>0.2003254251911018</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0001101657920794041</v>
+        <v>3.246686995490989e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0001958819024935358</v>
+        <v>8.850682884330539e-05</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0001530237153036247</v>
+        <v>6.048650977536561e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.002198212784960268</v>
+        <v>0.003238121710511044</v>
       </c>
       <c r="M26" t="n">
-        <v>0.007052498054371789</v>
+        <v>0.01033122389568578</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000057451801539</v>
+        <v>1.000123288125262</v>
       </c>
       <c r="O26" t="n">
-        <v>0.007352737497229967</v>
+        <v>0.01077104548550685</v>
       </c>
       <c r="P26" t="n">
-        <v>137.8174935638638</v>
+        <v>136.290338092526</v>
       </c>
       <c r="Q26" t="n">
-        <v>209.7311672310877</v>
+        <v>208.2040117597499</v>
       </c>
     </row>
   </sheetData>
